--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136673070</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136673073</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136673080</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136673083</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136673089</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136673091</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136673101</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136673104</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136673105</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136673108</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>136673109</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136673111</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136673114</v>
       </c>
       <c r="B24" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>136673116</v>
       </c>
       <c r="B25" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>136673117</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>136673118</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>136673121</v>
       </c>
       <c r="B28" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136673123</v>
       </c>
       <c r="B29" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136673070</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136673073</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136673080</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136673083</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136673089</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136673091</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136673101</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136673104</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136673105</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136673108</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>136673109</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136673111</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136673114</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>136673116</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>136673117</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>136673118</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>136673121</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136673123</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136673077</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>136673113</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136673070</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136673073</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136673080</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136673083</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136673089</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136673091</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136673101</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136673104</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136673105</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136673108</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>136673109</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136673111</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>136673114</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>136673116</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>136673117</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>136673118</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>136673121</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136673123</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -1839,11 +1839,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -1961,11 +1957,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2083,11 +2075,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2205,11 +2193,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2327,11 +2311,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2449,11 +2429,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2571,11 +2547,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2693,11 +2665,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2815,11 +2783,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -2937,11 +2901,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -3059,11 +3019,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -3181,11 +3137,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -3303,11 +3255,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -3425,11 +3373,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -3547,11 +3491,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -3669,11 +3609,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>
@@ -3796,16 +3732,8 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3923,11 +3851,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Glösa, Jmt</t>

--- a/artfynd/A 34245-2026 artfynd.xlsx
+++ b/artfynd/A 34245-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136673071</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136673074</v>
       </c>
       <c r="B3" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136673078</v>
       </c>
       <c r="B4" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136673082</v>
       </c>
       <c r="B5" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136673093</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136673095</v>
       </c>
       <c r="B7" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136673115</v>
       </c>
       <c r="B8" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136673120</v>
       </c>
       <c r="B9" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
